--- a/config/Excel/Gem_resonance.xlsx
+++ b/config/Excel/Gem_resonance.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B928026C-9E7B-4AE7-A69D-22BE4ABFC815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0824DC04-57B1-4CF8-8C17-1A8533316192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{648605E2-5E5E-4DEA-9FC5-F079B19D8924}"/>
+    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{648605E2-5E5E-4DEA-9FC5-F079B19D8924}"/>
   </bookViews>
   <sheets>
     <sheet name="Gem_resonance" sheetId="1" r:id="rId1"/>
@@ -110,9 +110,6 @@
     <t>魔法傷害</t>
   </si>
   <si>
-    <t>sapphire;pierceMagic;iolite;amethyst;garnet</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -173,9 +170,6 @@
     <t>物理傷害</t>
   </si>
   <si>
-    <t>ruby;piercePhys;opal;catseye</t>
-  </si>
-  <si>
     <t>6;4;5;5;5;4;4</t>
   </si>
   <si>
@@ -246,6 +240,14 @@
   </si>
   <si>
     <t>98415000</t>
+  </si>
+  <si>
+    <t>sapphire;pierceMagic;iolite;amethyst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ruby;piercePhys;opal;catseye;garnet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -656,12 +658,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE38E88C-0836-453A-9A17-7C0CD54834D2}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="14.77734375" customWidth="1"/>
+    <col min="1" max="11" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -696,7 +698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -731,7 +733,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -766,7 +768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -777,14 +779,14 @@
         <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G4" s="3" t="s">
         <v>13</v>
       </c>
@@ -801,25 +803,25 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="G5" s="3" t="s">
         <v>13</v>
       </c>
@@ -836,25 +838,25 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="G6" s="3" t="s">
         <v>13</v>
       </c>
@@ -871,25 +873,25 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="G7" s="3" t="s">
         <v>13</v>
       </c>
@@ -906,25 +908,25 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>13</v>
       </c>
@@ -941,25 +943,25 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>13</v>
       </c>
@@ -976,65 +978,65 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="C11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="H11" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>14</v>
@@ -1046,12 +1048,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
@@ -1066,10 +1068,10 @@
         <v>13</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>14</v>
@@ -1081,9 +1083,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>14</v>
@@ -1101,7 +1103,7 @@
         <v>13</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>14</v>
@@ -1116,12 +1118,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>13</v>
@@ -1136,10 +1138,10 @@
         <v>13</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>14</v>
@@ -1151,12 +1153,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>13</v>
@@ -1171,10 +1173,10 @@
         <v>13</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>14</v>
@@ -1186,173 +1188,173 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="B17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="C18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="I18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="I19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="I20" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>

--- a/config/Excel/Gem_resonance.xlsx
+++ b/config/Excel/Gem_resonance.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0824DC04-57B1-4CF8-8C17-1A8533316192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88488D8-CF3B-4165-A858-C39ED0C96B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{648605E2-5E5E-4DEA-9FC5-F079B19D8924}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{648605E2-5E5E-4DEA-9FC5-F079B19D8924}"/>
   </bookViews>
   <sheets>
     <sheet name="Gem_resonance" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="58">
   <si>
     <t>類型</t>
   </si>
@@ -194,52 +194,22 @@
     <t>1</t>
   </si>
   <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>15000</t>
-  </si>
-  <si>
-    <t>45000</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>135000</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
-    <t>405000</t>
-  </si>
-  <si>
-    <t>1215000</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
-    <t>3645000</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
-    <t>10935000</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
-    <t>32805000</t>
-  </si>
-  <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>98415000</t>
   </si>
   <si>
     <t>sapphire;pierceMagic;iolite;amethyst</t>
@@ -254,7 +224,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -287,6 +261,14 @@
       <family val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -305,12 +287,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -323,9 +308,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="千分位" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -779,7 +768,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>22</v>
@@ -954,7 +943,7 @@
         <v>41</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>22</v>
@@ -1032,8 +1021,8 @@
       <c r="F11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>50</v>
+      <c r="G11" s="4">
+        <v>5000</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>49</v>
@@ -1067,8 +1056,9 @@
       <c r="F12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>51</v>
+      <c r="G12" s="4">
+        <f>ROUND(G11*4.5,-3)</f>
+        <v>23000</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
@@ -1102,8 +1092,9 @@
       <c r="F13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>52</v>
+      <c r="G13" s="4">
+        <f t="shared" ref="G13:G20" si="0">ROUND(G12*4.5,-3)</f>
+        <v>104000</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>14</v>
@@ -1123,7 +1114,7 @@
         <v>48</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>13</v>
@@ -1137,11 +1128,12 @@
       <c r="F14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>54</v>
+      <c r="G14" s="4">
+        <f t="shared" si="0"/>
+        <v>468000</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>14</v>
@@ -1158,7 +1150,7 @@
         <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>13</v>
@@ -1172,11 +1164,12 @@
       <c r="F15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>56</v>
+      <c r="G15" s="4">
+        <f t="shared" si="0"/>
+        <v>2106000</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>14</v>
@@ -1207,8 +1200,9 @@
       <c r="F16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>57</v>
+      <c r="G16" s="4">
+        <f t="shared" si="0"/>
+        <v>9477000</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>46</v>
@@ -1228,7 +1222,7 @@
         <v>48</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>13</v>
@@ -1242,11 +1236,12 @@
       <c r="F17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>59</v>
+      <c r="G17" s="4">
+        <f t="shared" si="0"/>
+        <v>42647000</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>49</v>
@@ -1263,7 +1258,7 @@
         <v>48</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>13</v>
@@ -1277,11 +1272,12 @@
       <c r="F18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>61</v>
+      <c r="G18" s="4">
+        <f t="shared" si="0"/>
+        <v>191912000</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>49</v>
@@ -1298,7 +1294,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>13</v>
@@ -1312,11 +1308,12 @@
       <c r="F19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>63</v>
+      <c r="G19" s="4">
+        <f t="shared" si="0"/>
+        <v>863604000</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>49</v>
@@ -1333,7 +1330,7 @@
         <v>48</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
@@ -1347,11 +1344,12 @@
       <c r="F20" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>65</v>
+      <c r="G20" s="4">
+        <f t="shared" si="0"/>
+        <v>3886218000</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>49</v>
